--- a/templates/今日_Cafre_Berita_Broker/scripts.xlsx
+++ b/templates/今日_Cafre_Berita_Broker/scripts.xlsx
@@ -446,22 +446,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Trik Licik Broker Forex Ini Bikin Trader Global Tekor</t>
+          <t>Broker Mewah Ternyata Cuma Bot Bodong</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Broker forex LQH Markets sedang jadi sorotan. Bukan karena promo besar, tapi karena banjir keluhan dari berbagai platform!
-Di Trustpilot, sejumlah pengguna internasional menyampaikan pengalaman negatif terkait layanan, komunikasi, hingga masalah penarikan dana.
-Tak hanya global, paparan WikiFX juga mencatat laporan dari trader Indonesia dan Irak yang mengaku mengalami kendala setelah menggunakan broker ini.
-Jejak digitalnya juga terlihat di YouTube, dengan beberapa komentar pengguna yang memperingatkan trader lain untuk lebih berhati-hati.
-LQH Markets mengklaim memiliki regulasi di Saint Lucia. Namun, regulasi offshore sering menjadi perhatian karena tingkat perlindungannya berbeda dengan regulator besar seperti FCA atau ASIC.
-Apakah LQH Markets aman atau berisiko? Jangan hanya lihat bonus dan promosi. Cek regulasi, reputasi, dan pengalaman pengguna sebelum deposit. Cari tahu lebih lengkap di WikiFX.</t>
+          <t>Kelihatan kaya broker internasional yang mewah dan keren? Eits, jangan tertipu! Bisa jadi itu cuma broker bayangan!
+Regulator AS baru aja menjatuhkan denda total jutaan dolar ke penyedia white-label Netrios dan Red Acre.
+Modusnya? Mereka bikin mesin trading siap pakai, lengkap dari platform, eksekusi, sampai penampungan dana.
+Orang lain tinggal beli, pasang logo sendiri, lalu jualan CFD, Forex, dan Kripto ilegal tanpa izin resmi.
+Kelihatan beda perusahaan, padahal otak di belakangnya sama!
+Jangan cuma tanya bisa cuan gak. Cek legalitasnya, siapa yang pegang dana kamu, dan penyedianya jelas atau enggak. Biar dana kamu tetap aman!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>LQH Markets broker complaints Trustpilot WikiFX withdrawal offshore Saint Lucia regulation</t>
+          <t>white label broker Netrios Red Acre CFD forex crypto ilegal tanpa izin regulator AS denda platform trading</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
